--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484211_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484211_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.505</v>
+        <v>3.7194</v>
       </c>
       <c r="E2" t="n">
-        <v>0.838</v>
+        <v>1.1613</v>
       </c>
       <c r="F2" t="n">
-        <v>2.667</v>
+        <v>2.5581</v>
       </c>
       <c r="G2" t="n">
         <v>2.0211</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5514</v>
+        <v>-0.337</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4566</v>
+        <v>-0.1334</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0948</v>
+        <v>-0.2037</v>
       </c>
       <c r="V2" t="n">
         <v>0.2772</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8044</v>
+        <v>3.3844</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5118</v>
+        <v>2.0373</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2926</v>
+        <v>1.3471</v>
       </c>
       <c r="G3" t="n">
         <v>3.465</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1963</v>
+        <v>-0.6163</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6712</v>
+        <v>-0.1457</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5251</v>
+        <v>-0.4706</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8317</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6377</v>
+        <v>2.5543</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7712</v>
+        <v>1.9328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8666</v>
+        <v>0.6214</v>
       </c>
       <c r="G4" t="n">
         <v>3.5747</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1997</v>
+        <v>0.1162</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0246</v>
+        <v>0.137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2243</v>
+        <v>-0.0208</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9414</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3939</v>
+        <v>1.7518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4463</v>
+        <v>0.7496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9476</v>
+        <v>1.0021</v>
       </c>
       <c r="G5" t="n">
         <v>1.4924</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6845</v>
+        <v>-0.3267</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2421</v>
+        <v>0.0613</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4424</v>
+        <v>-0.388</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.167</v>
+        <v>1.6242</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0052</v>
+        <v>0.5713</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1618</v>
+        <v>1.0529</v>
       </c>
       <c r="G6" t="n">
         <v>2.486</v>
@@ -922,13 +922,13 @@
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.733</v>
+        <v>-0.2758</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6712</v>
+        <v>-0.1051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0618</v>
+        <v>-0.1707</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0611</v>
+        <v>0.5149</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1013</v>
+        <v>-0.4449</v>
       </c>
       <c r="F7" t="n">
         <v>0.9598</v>
@@ -1000,10 +1000,10 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>1.018</v>
+        <v>0.4719</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9383</v>
+        <v>0.3921</v>
       </c>
       <c r="U7" t="n">
         <v>0.07969999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9256</v>
+        <v>0.4145</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8223</v>
+        <v>0.175</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1033</v>
+        <v>0.2395</v>
       </c>
       <c r="G8" t="n">
         <v>0.6738</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6109</v>
+        <v>0.0998</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9659</v>
+        <v>0.3186</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.355</v>
+        <v>-0.2188</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0543</v>
+        <v>-0.2782</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5329</v>
+        <v>-1.8657</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4785</v>
+        <v>1.5875</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7287</v>
@@ -1156,13 +1156,13 @@
         <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8298</v>
+        <v>-0.0536</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6107</v>
+        <v>0.0566</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2191</v>
+        <v>-0.1102</v>
       </c>
       <c r="V9" t="n">
         <v>0.3321</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8016</v>
+        <v>-2.0777</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2149</v>
+        <v>-1.5182</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5867</v>
+        <v>-0.5595</v>
       </c>
       <c r="G10" t="n">
         <v>0.5433</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0457</v>
+        <v>-0.2304</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4128</v>
+        <v>0.1095</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3671</v>
+        <v>-0.3399</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6889</v>
+        <v>-3.0523</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9476</v>
+        <v>-6.3927</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2587</v>
+        <v>3.3404</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6032</v>
@@ -1312,13 +1312,13 @@
         <v>2.5395</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3049</v>
+        <v>-0.0584</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6495</v>
+        <v>0.2044</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3446</v>
+        <v>-0.2629</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9499</v>
+        <v>8.555299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1993</v>
+        <v>-3.594199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1492</v>
+        <v>12.1493</v>
       </c>
       <c r="G12" t="n">
         <v>9.072600000000001</v>
@@ -1390,10 +1390,10 @@
         <v>17.581</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8158</v>
+        <v>-1.2103</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2900999999999999</v>
+        <v>0.8953000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-2.1059</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.212300000000001</v>
+        <v>6.885</v>
       </c>
       <c r="E13" t="n">
-        <v>6.3739</v>
+        <v>4.3516</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8384</v>
+        <v>2.5334</v>
       </c>
       <c r="G13" t="n">
         <v>2.8534</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5077</v>
+        <v>2.1804</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1643</v>
+        <v>1.142</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3434</v>
+        <v>1.0384</v>
       </c>
       <c r="V13" t="n">
         <v>2.4373</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4857</v>
+        <v>4.0379</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4852</v>
+        <v>2.6874</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0005</v>
+        <v>1.3504</v>
       </c>
       <c r="G14" t="n">
         <v>0.7858000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0033</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0246</v>
+        <v>0.1776</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0213</v>
+        <v>0.3713</v>
       </c>
       <c r="V14" t="n">
         <v>0.5545</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0618</v>
+        <v>0.8273</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3355</v>
+        <v>0.8299</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2736</v>
+        <v>-0.0026</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1371</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1088</v>
+        <v>0.8742</v>
       </c>
       <c r="T15" t="n">
-        <v>0.831</v>
+        <v>0.3255</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2778</v>
+        <v>0.5488</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5806</v>
+        <v>-0.8054</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3385</v>
+        <v>-1.8329</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579</v>
+        <v>1.0275</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1113</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4925</v>
+        <v>0.2827</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4237</v>
+        <v>0.0819</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>0.2008</v>
       </c>
       <c r="V18" t="n">
         <v>1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.828</v>
+        <v>-1.2564</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5327</v>
+        <v>-0.2294</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2953</v>
+        <v>-1.027</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2057</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6576</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4237</v>
+        <v>-0.1203</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.234</v>
+        <v>0.0343</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9414</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7113</v>
+        <v>-2.2992</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0276</v>
+        <v>-3.4551</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3163</v>
+        <v>1.1559</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4993</v>
+        <v>-1.549</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9847</v>
+        <v>2.4569</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4854</v>
+        <v>-4.0059</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6908</v>
+        <v>1.7421</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6208</v>
+        <v>-2.6559</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4293</v>
+        <v>-0.6352</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2939</v>
+        <v>0.7148</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1022</v>
+        <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5591</v>
+        <v>0.2813</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4099</v>
+        <v>0.0297</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1492</v>
+        <v>0.2516</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="W20" t="n">
         <v>0.5545</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3463</v>
+        <v>-2.9892</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3651</v>
+        <v>-3.522</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0188</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.549</v>
+        <v>-0.4993</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4569</v>
+        <v>-0.9847</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.0059</v>
+        <v>0.4854</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7421</v>
+        <v>-0.6908</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6559</v>
+        <v>0.6208</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6352</v>
+        <v>-0.4293</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7148</v>
+        <v>-0.2939</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.35</v>
+        <v>-0.1354</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-4.1022</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7658</v>
+        <v>0.163</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8803</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8855</v>
+        <v>0.0673</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
         <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3949</v>
+        <v>-3.617</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5943</v>
+        <v>-4.4932</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1994</v>
+        <v>0.8762</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7854</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2421</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1899</v>
+        <v>0.291</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.432</v>
+        <v>0.2448</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1181</v>
+        <v>-5.632</v>
       </c>
       <c r="E23" t="n">
         <v>-6.4856</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3675</v>
+        <v>0.8536</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6937</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0803</v>
+        <v>0.4058</v>
       </c>
       <c r="T23" t="n">
         <v>0.08260000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.163</v>
+        <v>0.3232</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9498</v>
+        <v>-4.579400000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.1492</v>
+        <v>-12.1493</v>
       </c>
       <c r="F24" t="n">
-        <v>4.1995</v>
+        <v>7.5698</v>
       </c>
       <c r="G24" t="n">
         <v>-9.072699999999999</v>
@@ -2308,7 +2308,7 @@
         <v>-6.7389</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.2477</v>
+        <v>-6.247700000000001</v>
       </c>
       <c r="N24" t="n">
         <v>2.5266</v>
@@ -2326,13 +2326,13 @@
         <v>13.6741</v>
       </c>
       <c r="S24" t="n">
-        <v>1.815799999999999</v>
+        <v>5.186100000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1056</v>
+        <v>2.1057</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2900999999999998</v>
+        <v>3.0805</v>
       </c>
       <c r="V24" t="n">
         <v>3.2141</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484211_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484211_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +819,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7518</v>
+        <v>1.8349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7496</v>
+        <v>1.8349</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0021</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4924</v>
+        <v>1.8349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4405</v>
+        <v>1.2279</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0519</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6884</v>
+        <v>1.8349</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>1.2279</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6475</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8041</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3996</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3267</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0613</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.388</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6242</v>
+        <v>1.7518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5713</v>
+        <v>0.7496</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0529</v>
+        <v>1.0021</v>
       </c>
       <c r="G6" t="n">
-        <v>2.486</v>
+        <v>1.4924</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6032</v>
+        <v>0.4405</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0892</v>
+        <v>1.0519</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3293</v>
+        <v>0.6884</v>
       </c>
       <c r="K6" t="n">
-        <v>0.779</v>
+        <v>0.0409</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5503</v>
+        <v>0.6475</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8433</v>
+        <v>0.8041</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3822</v>
+        <v>0.3996</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>0.4045</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2758</v>
+        <v>-0.3267</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1051</v>
+        <v>0.0613</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1707</v>
+        <v>-0.388</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5149</v>
+        <v>0.4145</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4449</v>
+        <v>0.175</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9598</v>
+        <v>0.2395</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8518</v>
+        <v>0.6738</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4313</v>
+        <v>-0.3106</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5795</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.837</v>
+        <v>0.8331</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8774999999999999</v>
+        <v>0.6574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0.1757</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0148</v>
+        <v>-0.1593</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5538</v>
+        <v>-0.968</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5391</v>
+        <v>0.8087</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4719</v>
+        <v>0.0998</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3921</v>
+        <v>0.3186</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.2188</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4145</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.175</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2395</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6738</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3106</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9844000000000001</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8331</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6574</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1757</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1593</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.968</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8087</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0998</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3186</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2188</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2782</v>
+        <v>0.2079</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8657</v>
+        <v>-0.7519</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5875</v>
+        <v>0.9598</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7287</v>
+        <v>-1.1588</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8647</v>
+        <v>-1.7383</v>
       </c>
       <c r="I9" t="n">
-        <v>0.136</v>
+        <v>0.5795</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5548</v>
+        <v>-1.144</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3428</v>
+        <v>-1.1845</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.212</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1739</v>
+        <v>-0.0148</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5219</v>
+        <v>-0.5538</v>
       </c>
       <c r="O9" t="n">
-        <v>1.348</v>
+        <v>0.5391</v>
       </c>
       <c r="P9" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0536</v>
+        <v>0.4719</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0566</v>
+        <v>0.3921</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1102</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0777</v>
+        <v>-0.2108</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5182</v>
+        <v>-1.2636</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5595</v>
+        <v>1.0529</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5433</v>
+        <v>0.6511</v>
       </c>
       <c r="H10" t="n">
-        <v>0.112</v>
+        <v>-1.8312</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4313</v>
+        <v>2.4822</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0838</v>
+        <v>1.4944</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0781</v>
+        <v>-0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1619</v>
+        <v>1.9433</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4595</v>
+        <v>-0.8433</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1901</v>
+        <v>-1.3822</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2694</v>
+        <v>0.5389</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2304</v>
+        <v>-0.2758</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1095</v>
+        <v>-0.1051</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3399</v>
+        <v>-0.1707</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0523</v>
+        <v>-0.2782</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3927</v>
+        <v>-1.8657</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3404</v>
+        <v>1.5875</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6032</v>
+        <v>-1.7287</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5363</v>
+        <v>-1.8647</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0669</v>
+        <v>0.136</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.667</v>
+        <v>-1.5548</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.061</v>
+        <v>-0.3428</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.606</v>
+        <v>-1.212</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0638</v>
+        <v>-0.1739</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5247000000000001</v>
+        <v>-1.5219</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5391</v>
+        <v>1.348</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0584</v>
+        <v>-0.0536</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2044</v>
+        <v>0.0566</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2629</v>
+        <v>-0.1102</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.555299999999999</v>
+        <v>-2.0777</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.594199999999999</v>
+        <v>-1.5182</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1493</v>
+        <v>-0.5595</v>
       </c>
       <c r="G12" t="n">
-        <v>9.072600000000001</v>
+        <v>0.5433</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.4405</v>
+        <v>0.112</v>
       </c>
       <c r="I12" t="n">
-        <v>15.513</v>
+        <v>0.4313</v>
       </c>
       <c r="J12" t="n">
-        <v>6.2477</v>
+        <v>0.0838</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5265</v>
+        <v>-0.0781</v>
       </c>
       <c r="L12" t="n">
-        <v>8.7743</v>
+        <v>0.1619</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8251</v>
+        <v>0.4595</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.9139</v>
+        <v>0.1901</v>
       </c>
       <c r="O12" t="n">
-        <v>6.739000000000001</v>
+        <v>0.2694</v>
       </c>
       <c r="P12" t="n">
-        <v>3.906899999999999</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6738</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>17.581</v>
+        <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2103</v>
+        <v>-0.2304</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8953000000000001</v>
+        <v>0.1095</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1059</v>
+        <v>-0.3399</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.2141</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9368</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.151</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.885</v>
+        <v>-3.0523</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3516</v>
+        <v>-6.3927</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5334</v>
+        <v>3.3404</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8534</v>
+        <v>-2.6032</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2566</v>
+        <v>-2.5363</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4033</v>
+        <v>-0.0669</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8979</v>
+        <v>-3.667</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9512</v>
+        <v>-3.061</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0533</v>
+        <v>-0.606</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0445</v>
+        <v>1.0638</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3055</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.35</v>
+        <v>0.5391</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1804</v>
+        <v>-0.0584</v>
       </c>
       <c r="T13" t="n">
-        <v>1.142</v>
+        <v>0.2044</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0384</v>
+        <v>-0.2629</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0379</v>
+        <v>8.555199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6874</v>
+        <v>-3.594199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3504</v>
+        <v>12.1493</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7858000000000001</v>
+        <v>9.072600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5554</v>
+        <v>-6.4406</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7696</v>
+        <v>15.513</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9554</v>
+        <v>6.247700000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>1.375</v>
+        <v>-2.5266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5803</v>
+        <v>8.7743</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1696</v>
+        <v>2.8251</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1804</v>
+        <v>-3.9139</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.35</v>
+        <v>6.739</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1488</v>
+        <v>3.906899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-13.6738</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>17.581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5489000000000001</v>
+        <v>-1.2103</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1776</v>
+        <v>0.8953000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3713</v>
+        <v>-2.1059</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5545</v>
+        <v>-3.2141</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>2.9368</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-6.151</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8273</v>
+        <v>6.885</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8299</v>
+        <v>4.3516</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0026</v>
+        <v>2.5334</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1371</v>
+        <v>2.8534</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7114</v>
+        <v>4.2566</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8486</v>
+        <v>-1.4033</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2272</v>
+        <v>3.8979</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1867</v>
+        <v>3.9512</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>-0.0533</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3643</v>
+        <v>-1.0445</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.3055</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8891</v>
+        <v>-1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8742</v>
+        <v>2.1804</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3255</v>
+        <v>1.142</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5488</v>
+        <v>1.0384</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. PALLARES ARUMI</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1348</v>
+        <v>3.7309</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2.3804</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1348</v>
+        <v>1.3504</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1348</v>
+        <v>0.4788</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.2484</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1348</v>
+        <v>-0.7696</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.6484</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.068</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.5803</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1348</v>
+        <v>-1.1696</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.1804</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>-1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1776</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3713</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CARRERA PRAT</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1348</v>
+        <v>0.8273</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.8299</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1348</v>
+        <v>-0.0026</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1348</v>
+        <v>-1.1371</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.7114</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1348</v>
+        <v>-1.8486</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2272</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.1867</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1348</v>
+        <v>-1.3643</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>-1.8891</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.8742</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.3255</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.5488</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8054</v>
+        <v>0.307</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8329</v>
+        <v>0.307</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0275</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1113</v>
+        <v>0.307</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0727</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0387</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9614</v>
+        <v>0.307</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3277</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2551</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2827</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2008</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>P. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2564</v>
+        <v>0.1348</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2294</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.027</v>
+        <v>0.1348</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2057</v>
+        <v>0.1348</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5308</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1348</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3863</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3863</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8194</v>
+        <v>0.1348</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1445</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1348</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1203</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0343</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>J. CARRERA PRAT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2992</v>
+        <v>0.1348</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4551</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1559</v>
+        <v>0.1348</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.549</v>
+        <v>0.1348</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4569</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.0059</v>
+        <v>0.1348</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9137999999999999</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7421</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6559</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6352</v>
+        <v>0.1348</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7148</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.35</v>
+        <v>0.1348</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2813</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2516</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9892</v>
+        <v>-0.8054</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.522</v>
+        <v>-1.8329</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5328000000000001</v>
+        <v>1.0275</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4993</v>
+        <v>-2.1113</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9847</v>
+        <v>-1.0727</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4854</v>
+        <v>-1.0387</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.9614</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6908</v>
+        <v>-1.3277</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6208</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4293</v>
+        <v>-0.15</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>0.2551</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>-0.4051</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1022</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.163</v>
+        <v>0.2827</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0819</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0673</v>
+        <v>0.2008</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.617</v>
+        <v>-1.2564</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4932</v>
+        <v>-0.2294</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8762</v>
+        <v>-1.027</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7854</v>
+        <v>-1.2057</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0727</v>
+        <v>-0.5308</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7128</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6355</v>
+        <v>-0.3863</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3277</v>
+        <v>-0.3863</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.15</v>
+        <v>-0.8194</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2551</v>
+        <v>-0.1445</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5358000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.291</v>
+        <v>-0.1203</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2448</v>
+        <v>0.0343</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.632</v>
+        <v>-2.2992</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4856</v>
+        <v>-3.4551</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8536</v>
+        <v>1.1559</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6937</v>
+        <v>-1.549</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1208</v>
+        <v>2.4569</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.8144</v>
+        <v>-4.0059</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9386</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3914</v>
+        <v>1.7421</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.33</v>
+        <v>-2.6559</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.755</v>
+        <v>-0.6352</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7294</v>
+        <v>0.7148</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4844</v>
+        <v>-1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3441</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>-3.1255</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4058</v>
+        <v>0.2813</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0297</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3232</v>
+        <v>0.2516</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.579400000000002</v>
+        <v>-2.9892</v>
       </c>
       <c r="E24" t="n">
+        <v>-3.522</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.4993</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.9847</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6908</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.4293</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2939</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-4.1022</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M. CRUZ URBANEJA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.617</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.4932</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8762</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.7854</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.0727</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.7128</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.6355</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.3277</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2448</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D. VIDAL TEIXIDOR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.632</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.4856</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8536</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.6937</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.1208</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-4.8144</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.9386</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.755</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7294</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.4844</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484211_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.579399999999999</v>
+      </c>
+      <c r="E27" t="n">
         <v>-12.1493</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>7.5698</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-9.072699999999999</v>
       </c>
-      <c r="H24" t="n">
-        <v>6.440199999999999</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H27" t="n">
+        <v>6.4402</v>
+      </c>
+      <c r="I27" t="n">
         <v>-15.5132</v>
       </c>
-      <c r="J24" t="n">
-        <v>-2.8251</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J27" t="n">
+        <v>-2.825099999999999</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.9139</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>-6.7389</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>-6.247700000000001</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>2.5266</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>-8.7744</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-3.9067</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-17.581</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>13.6741</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>5.186100000000001</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>2.1057</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>3.0805</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>3.2141</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>6.151</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-2.9368</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
